--- a/preguntas/p4/excel/E4.xlsx
+++ b/preguntas/p4/excel/E4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\UNI 26-1\CONTROL ESTADISTICO DE PROCESOS\pc4\PC4-CEP-2026\preguntas\p4\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF8D0BD-A113-47FC-BECD-AE398E007E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9440640-B4D3-4267-93AF-46CC03295C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A2F2E121-3FCB-4196-93B8-6B1E85A12C78}"/>
   </bookViews>
